--- a/FIU_Phase2_Results.xlsx
+++ b/FIU_Phase2_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI-ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E77A1E0-4EDF-4164-9F89-BAEF227AAE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4E6422-7DD8-44C6-83C4-744F7371B4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="35" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -527,7 +527,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -657,7 +657,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -667,14 +667,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -683,74 +682,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3645,8 +3593,8 @@
     </cacheField>
     <cacheField name="Percent" numFmtId="0" formula=" 0" databaseField="0"/>
     <cacheField name="Field1" numFmtId="0" formula=" 0" databaseField="0"/>
-    <cacheField name="Field2" numFmtId="0" formula="'True Species' /'SVM Species' *100" databaseField="0"/>
-    <cacheField name="Percentage" numFmtId="0" formula="Fold /'SVM Species ✓'" databaseField="0"/>
+    <cacheField name="Field2" numFmtId="0" formula="'True Species'/'SVM Species'*100" databaseField="0"/>
+    <cacheField name="Percentage" numFmtId="0" formula="Fold/'SVM Species ✓'" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -12377,7 +12325,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8B6A64F-88C2-46C1-92AF-6FD1172F7EF4}" name="PivotTable6" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8B6A64F-88C2-46C1-92AF-6FD1172F7EF4}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B162" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -14072,19 +14020,19 @@
       <c r="A4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>75</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>132</v>
       </c>
     </row>
@@ -14092,19 +14040,19 @@
       <c r="A5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>47</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>18</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>20</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>0.9</v>
       </c>
     </row>
@@ -14112,19 +14060,19 @@
       <c r="A6" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>19</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>22</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>0.86399999999999999</v>
       </c>
     </row>
@@ -14132,19 +14080,19 @@
       <c r="A7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>16</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>20</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>0.8</v>
       </c>
     </row>
@@ -14152,19 +14100,19 @@
       <c r="A8" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>14</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>15</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>20</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>0.75</v>
       </c>
     </row>
@@ -14172,19 +14120,19 @@
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>16</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>23</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>0.69599999999999995</v>
       </c>
     </row>
@@ -14192,19 +14140,19 @@
       <c r="A10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>15</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>22</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <v>0.68200000000000005</v>
       </c>
     </row>
@@ -14212,19 +14160,19 @@
       <c r="A11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>36</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>12</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>20</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>0.6</v>
       </c>
     </row>
@@ -14232,19 +14180,19 @@
       <c r="A12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>15</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>9</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>20</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>0.45</v>
       </c>
     </row>
@@ -14252,19 +14200,19 @@
       <c r="A13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>9</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>8</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>20</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>0.4</v>
       </c>
     </row>
@@ -14272,19 +14220,19 @@
       <c r="A14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>8</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>20</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <v>0.4</v>
       </c>
     </row>
@@ -14292,19 +14240,19 @@
       <c r="A15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>9</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>5</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>23</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>0.217</v>
       </c>
     </row>
@@ -14312,19 +14260,19 @@
       <c r="A16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>4</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>20</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>0.2</v>
       </c>
     </row>
@@ -14332,19 +14280,19 @@
       <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>45</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>3</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>20</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="13">
         <v>0.15</v>
       </c>
     </row>
@@ -14352,7 +14300,7 @@
       <c r="A18" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>3</v>
       </c>
     </row>
@@ -14360,7 +14308,7 @@
       <c r="A19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>37</v>
       </c>
     </row>
@@ -14368,7 +14316,7 @@
       <c r="A20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20">
         <v>2</v>
       </c>
     </row>
@@ -14376,19 +14324,19 @@
       <c r="A21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21">
         <v>3</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="16" t="s">
         <v>132</v>
       </c>
     </row>
@@ -14396,19 +14344,19 @@
       <c r="A22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22">
         <v>49</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="6">
         <v>20</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="6">
         <v>25</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="7">
         <v>0.8</v>
       </c>
     </row>
@@ -14416,19 +14364,19 @@
       <c r="A23" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23">
         <v>42</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="9">
         <v>18</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="9">
         <v>25</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="10">
         <v>0.72</v>
       </c>
     </row>
@@ -14436,19 +14384,19 @@
       <c r="A24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24">
         <v>7</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="6">
         <v>17</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="6">
         <v>25</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="7">
         <v>0.68</v>
       </c>
     </row>
@@ -14456,19 +14404,19 @@
       <c r="A25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25">
         <v>60</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="9">
         <v>16</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="9">
         <v>25</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="10">
         <v>0.64</v>
       </c>
     </row>
@@ -14476,19 +14424,19 @@
       <c r="A26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26">
         <v>51</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="6">
         <v>16</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="6">
         <v>25</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="7">
         <v>0.64</v>
       </c>
     </row>
@@ -14496,19 +14444,19 @@
       <c r="A27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27">
         <v>9</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="9">
         <v>15</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="9">
         <v>25</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="10">
         <v>0.6</v>
       </c>
     </row>
@@ -14516,19 +14464,19 @@
       <c r="A28" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28">
         <v>60</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="6">
         <v>13</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="6">
         <v>25</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="12">
         <v>0.52</v>
       </c>
     </row>
@@ -14536,19 +14484,19 @@
       <c r="A29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29">
         <v>6</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="9">
         <v>10</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="9">
         <v>25</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="11">
         <v>0.4</v>
       </c>
     </row>
@@ -14556,7 +14504,7 @@
       <c r="A30" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30">
         <v>14</v>
       </c>
     </row>
@@ -14564,7 +14512,7 @@
       <c r="A31" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31">
         <v>19</v>
       </c>
     </row>
@@ -14572,7 +14520,7 @@
       <c r="A32" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32">
         <v>2</v>
       </c>
     </row>
@@ -14580,7 +14528,7 @@
       <c r="A33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33">
         <v>9</v>
       </c>
     </row>
@@ -14588,7 +14536,7 @@
       <c r="A34" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34">
         <v>10</v>
       </c>
     </row>
@@ -14596,19 +14544,19 @@
       <c r="A35" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35">
         <v>53</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G35" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -14616,19 +14564,19 @@
       <c r="A36" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36">
         <v>5</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="6">
         <v>14</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="6">
         <v>16</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="7">
         <v>0.875</v>
       </c>
     </row>
@@ -14636,19 +14584,19 @@
       <c r="A37" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37">
         <v>21</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="9">
         <v>12</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="9">
         <v>15</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="10">
         <v>0.8</v>
       </c>
     </row>
@@ -14656,19 +14604,19 @@
       <c r="A38" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38">
         <v>21</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="6">
         <v>12</v>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="6">
         <v>16</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="7">
         <v>0.75</v>
       </c>
     </row>
@@ -14676,19 +14624,19 @@
       <c r="A39" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39">
         <v>3</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="9">
         <v>10</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="9">
         <v>16</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="10">
         <v>0.625</v>
       </c>
     </row>
@@ -14696,19 +14644,19 @@
       <c r="A40" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40">
         <v>3</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="6">
         <v>10</v>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="6">
         <v>17</v>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="12">
         <v>0.58799999999999997</v>
       </c>
     </row>
@@ -14716,19 +14664,19 @@
       <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41">
         <v>48</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="9">
         <v>6</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="9">
         <v>13</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="11">
         <v>0.46200000000000002</v>
       </c>
     </row>
@@ -14736,19 +14684,19 @@
       <c r="A42" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42">
         <v>11</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="6">
         <v>7</v>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="6">
         <v>18</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="13">
         <v>0.38900000000000001</v>
       </c>
     </row>
@@ -14756,7 +14704,7 @@
       <c r="A43" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43">
         <v>4</v>
       </c>
     </row>
@@ -14764,7 +14712,7 @@
       <c r="A44" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44">
         <v>33</v>
       </c>
     </row>
@@ -14772,7 +14720,7 @@
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45">
         <v>66</v>
       </c>
     </row>
@@ -14780,7 +14728,7 @@
       <c r="A46" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46">
         <v>49</v>
       </c>
     </row>
@@ -14788,7 +14736,7 @@
       <c r="A47" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47">
         <v>6</v>
       </c>
     </row>
@@ -14796,7 +14744,7 @@
       <c r="A48" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48">
         <v>11</v>
       </c>
     </row>
@@ -14804,7 +14752,7 @@
       <c r="A49" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49">
         <v>75</v>
       </c>
     </row>
@@ -14812,7 +14760,7 @@
       <c r="A50" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50">
         <v>38</v>
       </c>
     </row>
@@ -14820,7 +14768,7 @@
       <c r="A51" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51">
         <v>19</v>
       </c>
     </row>
@@ -14828,7 +14776,7 @@
       <c r="A52" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52">
         <v>13</v>
       </c>
     </row>
@@ -14836,7 +14784,7 @@
       <c r="A53" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53">
         <v>5</v>
       </c>
     </row>
@@ -14844,7 +14792,7 @@
       <c r="A54" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54">
         <v>75</v>
       </c>
     </row>
@@ -14852,7 +14800,7 @@
       <c r="A55" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55">
         <v>3</v>
       </c>
     </row>
@@ -14860,7 +14808,7 @@
       <c r="A56" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56">
         <v>63</v>
       </c>
     </row>
@@ -14868,7 +14816,7 @@
       <c r="A57" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57">
         <v>9</v>
       </c>
     </row>
@@ -14876,7 +14824,7 @@
       <c r="A58" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58">
         <v>54</v>
       </c>
     </row>
@@ -14884,7 +14832,7 @@
       <c r="A59" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59">
         <v>5</v>
       </c>
     </row>
@@ -14892,7 +14840,7 @@
       <c r="A60" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60">
         <v>1</v>
       </c>
     </row>
@@ -14900,7 +14848,7 @@
       <c r="A61" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61">
         <v>14</v>
       </c>
     </row>
@@ -14908,7 +14856,7 @@
       <c r="A62" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62">
         <v>4</v>
       </c>
     </row>
@@ -14916,7 +14864,7 @@
       <c r="A63" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63">
         <v>30</v>
       </c>
     </row>
@@ -14924,7 +14872,7 @@
       <c r="A64" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64">
         <v>60</v>
       </c>
     </row>
@@ -14932,7 +14880,7 @@
       <c r="A65" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65">
         <v>1</v>
       </c>
     </row>
@@ -14940,7 +14888,7 @@
       <c r="A66" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66">
         <v>49</v>
       </c>
     </row>
@@ -14948,7 +14896,7 @@
       <c r="A67" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67">
         <v>6</v>
       </c>
     </row>
@@ -14956,7 +14904,7 @@
       <c r="A68" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68">
         <v>1</v>
       </c>
     </row>
@@ -14964,7 +14912,7 @@
       <c r="A69" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69">
         <v>3</v>
       </c>
     </row>
@@ -14972,7 +14920,7 @@
       <c r="A70" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70">
         <v>75</v>
       </c>
     </row>
@@ -14980,7 +14928,7 @@
       <c r="A71" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71">
         <v>4</v>
       </c>
     </row>
@@ -14988,7 +14936,7 @@
       <c r="A72" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72">
         <v>2</v>
       </c>
     </row>
@@ -14996,7 +14944,7 @@
       <c r="A73" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73">
         <v>42</v>
       </c>
     </row>
@@ -15004,7 +14952,7 @@
       <c r="A74" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74">
         <v>20</v>
       </c>
     </row>
@@ -15012,7 +14960,7 @@
       <c r="A75" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="5">
+      <c r="B75">
         <v>7</v>
       </c>
     </row>
@@ -15020,7 +14968,7 @@
       <c r="A76" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B76">
         <v>60</v>
       </c>
     </row>
@@ -15028,7 +14976,7 @@
       <c r="A77" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B77">
         <v>5</v>
       </c>
     </row>
@@ -15036,7 +14984,7 @@
       <c r="A78" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B78">
         <v>1</v>
       </c>
     </row>
@@ -15044,7 +14992,7 @@
       <c r="A79" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="5">
+      <c r="B79">
         <v>49</v>
       </c>
     </row>
@@ -15052,7 +15000,7 @@
       <c r="A80" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="5">
+      <c r="B80">
         <v>5</v>
       </c>
     </row>
@@ -15060,7 +15008,7 @@
       <c r="A81" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="5">
+      <c r="B81">
         <v>69</v>
       </c>
     </row>
@@ -15068,7 +15016,7 @@
       <c r="A82" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B82" s="5">
+      <c r="B82">
         <v>3</v>
       </c>
     </row>
@@ -15076,7 +15024,7 @@
       <c r="A83" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83">
         <v>15</v>
       </c>
     </row>
@@ -15084,7 +15032,7 @@
       <c r="A84" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B84">
         <v>44</v>
       </c>
     </row>
@@ -15092,7 +15040,7 @@
       <c r="A85" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="5">
+      <c r="B85">
         <v>1</v>
       </c>
     </row>
@@ -15100,7 +15048,7 @@
       <c r="A86" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B86">
         <v>6</v>
       </c>
     </row>
@@ -15108,7 +15056,7 @@
       <c r="A87" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B87">
         <v>75</v>
       </c>
     </row>
@@ -15116,7 +15064,7 @@
       <c r="A88" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B88">
         <v>3</v>
       </c>
     </row>
@@ -15124,7 +15072,7 @@
       <c r="A89" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B89">
         <v>19</v>
       </c>
     </row>
@@ -15132,7 +15080,7 @@
       <c r="A90" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90">
         <v>53</v>
       </c>
     </row>
@@ -15140,7 +15088,7 @@
       <c r="A91" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91">
         <v>75</v>
       </c>
     </row>
@@ -15148,7 +15096,7 @@
       <c r="A92" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B92">
         <v>6</v>
       </c>
     </row>
@@ -15156,7 +15104,7 @@
       <c r="A93" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="5">
+      <c r="B93">
         <v>20</v>
       </c>
     </row>
@@ -15164,7 +15112,7 @@
       <c r="A94" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B94" s="5">
+      <c r="B94">
         <v>1</v>
       </c>
     </row>
@@ -15172,7 +15120,7 @@
       <c r="A95" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B95" s="5">
+      <c r="B95">
         <v>28</v>
       </c>
     </row>
@@ -15180,7 +15128,7 @@
       <c r="A96" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B96" s="5">
+      <c r="B96">
         <v>15</v>
       </c>
     </row>
@@ -15188,7 +15136,7 @@
       <c r="A97" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="5">
+      <c r="B97">
         <v>5</v>
       </c>
     </row>
@@ -15196,7 +15144,7 @@
       <c r="A98" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B98" s="5">
+      <c r="B98">
         <v>66</v>
       </c>
     </row>
@@ -15204,7 +15152,7 @@
       <c r="A99" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B99">
         <v>8</v>
       </c>
     </row>
@@ -15212,7 +15160,7 @@
       <c r="A100" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B100">
         <v>14</v>
       </c>
     </row>
@@ -15220,7 +15168,7 @@
       <c r="A101" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B101">
         <v>4</v>
       </c>
     </row>
@@ -15228,7 +15176,7 @@
       <c r="A102" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B102">
         <v>18</v>
       </c>
     </row>
@@ -15236,7 +15184,7 @@
       <c r="A103" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B103" s="5">
+      <c r="B103">
         <v>10</v>
       </c>
     </row>
@@ -15244,7 +15192,7 @@
       <c r="A104" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B104" s="5">
+      <c r="B104">
         <v>9</v>
       </c>
     </row>
@@ -15252,7 +15200,7 @@
       <c r="A105" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B105" s="5">
+      <c r="B105">
         <v>3</v>
       </c>
     </row>
@@ -15260,7 +15208,7 @@
       <c r="A106" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B106" s="5">
+      <c r="B106">
         <v>75</v>
       </c>
     </row>
@@ -15268,7 +15216,7 @@
       <c r="A107" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B107" s="5">
+      <c r="B107">
         <v>2</v>
       </c>
     </row>
@@ -15276,7 +15224,7 @@
       <c r="A108" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B108" s="5">
+      <c r="B108">
         <v>11</v>
       </c>
     </row>
@@ -15284,7 +15232,7 @@
       <c r="A109" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B109" s="5">
+      <c r="B109">
         <v>1</v>
       </c>
     </row>
@@ -15292,7 +15240,7 @@
       <c r="A110" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B110" s="5">
+      <c r="B110">
         <v>53</v>
       </c>
     </row>
@@ -15300,7 +15248,7 @@
       <c r="A111" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B111" s="5">
+      <c r="B111">
         <v>8</v>
       </c>
     </row>
@@ -15308,7 +15256,7 @@
       <c r="A112" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B112" s="5">
+      <c r="B112">
         <v>46</v>
       </c>
     </row>
@@ -15316,7 +15264,7 @@
       <c r="A113" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B113" s="5">
+      <c r="B113">
         <v>7</v>
       </c>
     </row>
@@ -15324,7 +15272,7 @@
       <c r="A114" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B114" s="5">
+      <c r="B114">
         <v>4</v>
       </c>
     </row>
@@ -15332,7 +15280,7 @@
       <c r="A115" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B115">
         <v>1</v>
       </c>
     </row>
@@ -15340,7 +15288,7 @@
       <c r="A116" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B116" s="5">
+      <c r="B116">
         <v>2</v>
       </c>
     </row>
@@ -15348,7 +15296,7 @@
       <c r="A117" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B117" s="5">
+      <c r="B117">
         <v>32</v>
       </c>
     </row>
@@ -15356,7 +15304,7 @@
       <c r="A118" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B118" s="5">
+      <c r="B118">
         <v>60</v>
       </c>
     </row>
@@ -15364,7 +15312,7 @@
       <c r="A119" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B119" s="5">
+      <c r="B119">
         <v>31</v>
       </c>
     </row>
@@ -15372,7 +15320,7 @@
       <c r="A120" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B120" s="5">
+      <c r="B120">
         <v>21</v>
       </c>
     </row>
@@ -15380,7 +15328,7 @@
       <c r="A121" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B121" s="5">
+      <c r="B121">
         <v>8</v>
       </c>
     </row>
@@ -15388,7 +15336,7 @@
       <c r="A122" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B122" s="5">
+      <c r="B122">
         <v>60</v>
       </c>
     </row>
@@ -15396,7 +15344,7 @@
       <c r="A123" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B123" s="5">
+      <c r="B123">
         <v>4</v>
       </c>
     </row>
@@ -15404,7 +15352,7 @@
       <c r="A124" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="5">
+      <c r="B124">
         <v>7</v>
       </c>
     </row>
@@ -15412,7 +15360,7 @@
       <c r="A125" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B125" s="5">
+      <c r="B125">
         <v>24</v>
       </c>
     </row>
@@ -15420,7 +15368,7 @@
       <c r="A126" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B126" s="5">
+      <c r="B126">
         <v>17</v>
       </c>
     </row>
@@ -15428,7 +15376,7 @@
       <c r="A127" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B127" s="5">
+      <c r="B127">
         <v>8</v>
       </c>
     </row>
@@ -15436,7 +15384,7 @@
       <c r="A128" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B128" s="5">
+      <c r="B128">
         <v>60</v>
       </c>
     </row>
@@ -15444,7 +15392,7 @@
       <c r="A129" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B129" s="5">
+      <c r="B129">
         <v>4</v>
       </c>
     </row>
@@ -15452,7 +15400,7 @@
       <c r="A130" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B130" s="5">
+      <c r="B130">
         <v>5</v>
       </c>
     </row>
@@ -15460,7 +15408,7 @@
       <c r="A131" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B131" s="5">
+      <c r="B131">
         <v>1</v>
       </c>
     </row>
@@ -15468,7 +15416,7 @@
       <c r="A132" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B132" s="5">
+      <c r="B132">
         <v>3</v>
       </c>
     </row>
@@ -15476,7 +15424,7 @@
       <c r="A133" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B133" s="5">
+      <c r="B133">
         <v>37</v>
       </c>
     </row>
@@ -15484,7 +15432,7 @@
       <c r="A134" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B134" s="5">
+      <c r="B134">
         <v>2</v>
       </c>
     </row>
@@ -15492,7 +15440,7 @@
       <c r="A135" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B135" s="5">
+      <c r="B135">
         <v>8</v>
       </c>
     </row>
@@ -15500,7 +15448,7 @@
       <c r="A136" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B136" s="5">
+      <c r="B136">
         <v>60</v>
       </c>
     </row>
@@ -15508,7 +15456,7 @@
       <c r="A137" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B137" s="5">
+      <c r="B137">
         <v>2</v>
       </c>
     </row>
@@ -15516,7 +15464,7 @@
       <c r="A138" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B138" s="5">
+      <c r="B138">
         <v>6</v>
       </c>
     </row>
@@ -15524,7 +15472,7 @@
       <c r="A139" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B139" s="5">
+      <c r="B139">
         <v>5</v>
       </c>
     </row>
@@ -15532,7 +15480,7 @@
       <c r="A140" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B140" s="5">
+      <c r="B140">
         <v>12</v>
       </c>
     </row>
@@ -15540,7 +15488,7 @@
       <c r="A141" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B141" s="5">
+      <c r="B141">
         <v>3</v>
       </c>
     </row>
@@ -15548,7 +15496,7 @@
       <c r="A142" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B142" s="5">
+      <c r="B142">
         <v>19</v>
       </c>
     </row>
@@ -15556,7 +15504,7 @@
       <c r="A143" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B143" s="5">
+      <c r="B143">
         <v>9</v>
       </c>
     </row>
@@ -15564,7 +15512,7 @@
       <c r="A144" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B144" s="5">
+      <c r="B144">
         <v>4</v>
       </c>
     </row>
@@ -15572,7 +15520,7 @@
       <c r="A145" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B145" s="5">
+      <c r="B145">
         <v>60</v>
       </c>
     </row>
@@ -15580,7 +15528,7 @@
       <c r="A146" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B146" s="5">
+      <c r="B146">
         <v>6</v>
       </c>
     </row>
@@ -15588,7 +15536,7 @@
       <c r="A147" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B147" s="5">
+      <c r="B147">
         <v>13</v>
       </c>
     </row>
@@ -15596,7 +15544,7 @@
       <c r="A148" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B148" s="5">
+      <c r="B148">
         <v>5</v>
       </c>
     </row>
@@ -15604,7 +15552,7 @@
       <c r="A149" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B149" s="5">
+      <c r="B149">
         <v>8</v>
       </c>
     </row>
@@ -15612,7 +15560,7 @@
       <c r="A150" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B150" s="5">
+      <c r="B150">
         <v>4</v>
       </c>
     </row>
@@ -15620,7 +15568,7 @@
       <c r="A151" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B151" s="5">
+      <c r="B151">
         <v>6</v>
       </c>
     </row>
@@ -15628,7 +15576,7 @@
       <c r="A152" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B152" s="5">
+      <c r="B152">
         <v>18</v>
       </c>
     </row>
@@ -15636,7 +15584,7 @@
       <c r="A153" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B153" s="5">
+      <c r="B153">
         <v>75</v>
       </c>
     </row>
@@ -15644,7 +15592,7 @@
       <c r="A154" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B154" s="5">
+      <c r="B154">
         <v>6</v>
       </c>
     </row>
@@ -15652,7 +15600,7 @@
       <c r="A155" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B155" s="5">
+      <c r="B155">
         <v>18</v>
       </c>
     </row>
@@ -15660,7 +15608,7 @@
       <c r="A156" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B156" s="5">
+      <c r="B156">
         <v>51</v>
       </c>
     </row>
@@ -15668,7 +15616,7 @@
       <c r="A157" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B157" s="5">
+      <c r="B157">
         <v>69</v>
       </c>
     </row>
@@ -15676,7 +15624,7 @@
       <c r="A158" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B158" s="5">
+      <c r="B158">
         <v>3</v>
       </c>
     </row>
@@ -15684,7 +15632,7 @@
       <c r="A159" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B159" s="5">
+      <c r="B159">
         <v>5</v>
       </c>
     </row>
@@ -15692,7 +15640,7 @@
       <c r="A160" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B160" s="5">
+      <c r="B160">
         <v>1</v>
       </c>
     </row>
@@ -15700,7 +15648,7 @@
       <c r="A161" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B161" s="5">
+      <c r="B161">
         <v>60</v>
       </c>
     </row>
@@ -15708,7 +15656,7 @@
       <c r="A162" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B162" s="5">
+      <c r="B162">
         <v>1741</v>
       </c>
     </row>
@@ -15725,6 +15673,13 @@
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
